--- a/results/Int All Data -1.0/Rando_fi_explain.xlsx
+++ b/results/Int All Data -1.0/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0001630829770714049</v>
+        <v>0.0003119997915681105</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0001475643198862764</v>
+        <v>0.0003085494083478579</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001335063784287345</v>
+        <v>-0.0005652708113655102</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0005744860857449362</v>
+        <v>-0.0002833558657723955</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0003029624028564082</v>
+        <v>-8.798991523598082e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006366960917359233</v>
+        <v>0.002123265481204624</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003270358566137177</v>
+        <v>-0.0001819679197255897</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0006938641280957182</v>
+        <v>0.0002394071289239486</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0005353147343190867</v>
+        <v>-0.0001893189234050874</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0004385782522844673</v>
+        <v>0.0003006787973432723</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0002711278106385429</v>
+        <v>2.73711740788496e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.001631405624781491</v>
+        <v>-0.0002210431140178315</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0002227407990627773</v>
+        <v>-0.0002825970187882277</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.00186051638780222</v>
+        <v>-0.0009727621465188763</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005574779819999619</v>
+        <v>0.0004218112575461452</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00324721331061961</v>
+        <v>0.004154177457945736</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0007247180253111686</v>
+        <v>-0.0001637306331340216</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001003357507692176</v>
+        <v>-0.0006458088066083077</v>
       </c>
       <c r="T3" t="n">
-        <v>8.297525788972781e-06</v>
+        <v>0.0006475562184524243</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004202126245126159</v>
+        <v>0.0006554345461773435</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0005697642743301268</v>
+        <v>-0.0008393082428390863</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0006815318283927908</v>
+        <v>-0.000260056918824394</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001520899960000422</v>
+        <v>0.000582984368984539</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0005346839949462456</v>
+        <v>-0.0001487541939711723</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002736988580748686</v>
+        <v>0.001527908665219772</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002745395075990705</v>
+        <v>0.002815010222678614</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0007215700597323905</v>
+        <v>-0.0001699013433542818</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.002309008244378733</v>
+        <v>-0.0007393651191130245</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003062810438795989</v>
+        <v>0.003846545869862675</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005023974493591149</v>
+        <v>0.006729386892981295</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0009689777040220295</v>
+        <v>0.001633320272024778</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0005363842980456234</v>
+        <v>-7.430748254410704e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0003031477948419802</v>
+        <v>0.0003102752407100551</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.000117405237830418</v>
+        <v>0.001207668381069962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5.610659839537773e-06</v>
+        <v>0.002013263293347789</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.012140333495696</v>
+        <v>0.01383083671225099</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0001565142233125904</v>
+        <v>0.0003674043934759741</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003535834577714889</v>
+        <v>0.002206518839450323</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001055680461367855</v>
+        <v>-0.0005530662339810709</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0005303801951357213</v>
+        <v>-0.001264803982073877</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.001043440759112974</v>
+        <v>-0.0001173445375781957</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.003229453249457409</v>
+        <v>0.001724298357804641</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.008215621855615481</v>
+        <v>0.007172888269671868</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005805144502688655</v>
+        <v>-0.0008273789675921062</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0007373753043886166</v>
+        <v>-0.0001537467843921892</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0001076849622129938</v>
+        <v>0.0003163199798318172</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0008056325405939701</v>
+        <v>0.0002680651596721706</v>
       </c>
       <c r="AW3" t="n">
-        <v>-7.870163229172884e-05</v>
+        <v>0.0004781384788686949</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.68659957441564e-05</v>
+        <v>9.133985268687362e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.002774117978789905</v>
+        <v>0.001188995923038258</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0002083820181188489</v>
+        <v>0.0001291842626574869</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.002949257792244934</v>
+        <v>0.001988460670084105</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002935111375330303</v>
+        <v>0.003047240800967379</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0002295331707814252</v>
+        <v>-0.0001152464640472439</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0002108890759977644</v>
+        <v>-0.0001736857887068688</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0002274698787661812</v>
+        <v>0.001022113952521793</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.45901330084375e-05</v>
+        <v>0.001303013197208497</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002482234802720493</v>
+        <v>-0.001155360162511013</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.469653396143913e-05</v>
+        <v>2.003021552786197e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.006979596251490071</v>
+        <v>0.006356139330012442</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0007614151148963155</v>
+        <v>0.0009480143451294311</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0005982402345872684</v>
+        <v>-0.001013517452382785</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0002829880929321427</v>
+        <v>-0.0003272937482522953</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001444298361730962</v>
+        <v>-0.0001637407602087616</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.0001871418801375935</v>
+        <v>0.0005604785961889826</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001559932906881004</v>
+        <v>-0.0001106743370202623</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0007614488627238658</v>
+        <v>0.0002397835392605497</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001080185639795284</v>
+        <v>0.0004517050717918124</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0001546986711633735</v>
+        <v>0.0009665719793894546</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0002992315156678949</v>
+        <v>0.0001464451418600754</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.001002241702989627</v>
+        <v>0.00113090530188074</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001599068602227476</v>
+        <v>-0.001584627111423738</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.687549024431469e-06</v>
+        <v>9.704515644842648e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.000847443656633947</v>
+        <v>-0.0003087809216881188</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0006886931910429595</v>
+        <v>0.0003331854027049142</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.000376701777108095</v>
+        <v>-5.901924065550229e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0007066827627369743</v>
+        <v>-9.210967844988766e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0004149125828160361</v>
+        <v>0.001332069240013374</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0008342387815410525</v>
+        <v>0.0001171507865451793</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.000870243862853326</v>
+        <v>0.0001636992175805718</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0009518261601587308</v>
+        <v>-0.0003345090442937049</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0002691150981472256</v>
+        <v>-0.0001775559730706288</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0004404737267785619</v>
+        <v>0.0004218218118381457</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0009690839514783212</v>
+        <v>-0.0002411431083269189</v>
       </c>
       <c r="CI3" t="n">
-        <v>-9.552634710017279e-06</v>
+        <v>0.0007711119149224665</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-1.603585494502929e-07</v>
+        <v>8.656200712282567e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0001204561981731977</v>
+        <v>0.0002498376560354287</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.004021405076061074</v>
+        <v>-0.001736032619125981</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001008775473026218</v>
+        <v>0.0005815772162833533</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001105691549781017</v>
+        <v>0.0002160953365430806</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0003463424112362968</v>
+        <v>0.0005984114698663212</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.0001660229025364634</v>
+        <v>-0.0001658050604060646</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001131918197648743</v>
+        <v>0.001166060899324299</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.00216733316188879</v>
+        <v>-0.002660969050199346</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.003485213410214253</v>
+        <v>-0.002086588054534179</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0006956624473146466</v>
+        <v>-0.001492354362673057</v>
       </c>
       <c r="CU3" t="n">
-        <v>-4.760348949599758e-05</v>
+        <v>-7.587871336872666e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>-3.32777354285829e-06</v>
+        <v>1.430036886280628e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.001561772095806372</v>
+        <v>-0.001564804550782734</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.002211956372957285</v>
+        <v>-0.001950699002137872</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0001837544634927901</v>
+        <v>-0.0003808188558862047</v>
       </c>
       <c r="DA3" t="n">
-        <v>-6.625833832190618e-05</v>
+        <v>2.442085666450102e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001637000911393704</v>
+        <v>0.0004963760790966942</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.002077541649988525</v>
+        <v>-0.001556083076814169</v>
       </c>
       <c r="DD3" t="n">
-        <v>6.622789098159277e-05</v>
+        <v>-4.242233045555044e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0006428802433024816</v>
+        <v>0.0003459136140194463</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.002192704187965043</v>
+        <v>-0.002044808768961278</v>
       </c>
       <c r="DG3" t="n">
-        <v>5.744017702129728e-05</v>
+        <v>6.469985694661732e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.003016184870866272</v>
+        <v>-0.001046237542082819</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.707096065440173e-05</v>
+        <v>3.750898964087432e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0006904419249145622</v>
+        <v>0.0005233933312384398</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0003055764091908108</v>
+        <v>-0.001804897059115401</v>
       </c>
       <c r="DL3" t="n">
-        <v>7.790913162361911e-05</v>
+        <v>-7.711822017160807e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-7.974521239438646e-05</v>
+        <v>-0.0001497814285059018</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0008528760561877669</v>
+        <v>-0.001406480783677895</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001416295108383193</v>
+        <v>-0.0008761371914735984</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.002860600265329598</v>
+        <v>-0.002034892772407436</v>
       </c>
       <c r="DQ3" t="n">
-        <v>3.823738097545104e-05</v>
+        <v>3.433489156770663e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.628651824423958e-06</v>
+        <v>0.00010516547969038</v>
       </c>
       <c r="DS3" t="n">
-        <v>-3.105525003944899e-05</v>
+        <v>-4.761711264085089e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.001360041874420781</v>
+        <v>-0.001107274149910158</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.003056939921737892</v>
+        <v>-0.0007570836886474809</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-4.990079388864976e-05</v>
+        <v>0.0002711154569362851</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0003264748037906107</v>
+        <v>0.0001788320434949353</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0005593096231632344</v>
+        <v>-0.002561016216474949</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0001440641609642634</v>
+        <v>-5.080645093473392e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.00102875486283482</v>
+        <v>-0.001345735399887937</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.001766109542045802</v>
+        <v>-0.001241604482333872</v>
       </c>
       <c r="EC3" t="n">
-        <v>7.320400690395302e-05</v>
+        <v>-0.0005708243791234148</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0007455992057601301</v>
+        <v>0.0006433998550743868</v>
       </c>
       <c r="EE3" t="n">
-        <v>8.071556886593e-05</v>
+        <v>1.175753478464769e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>5.974687391341327e-06</v>
+        <v>0.0003948312870490012</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0003884139161804056</v>
+        <v>-0.0005755839402459395</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.0004843332163841607</v>
+        <v>5.421676791692143e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.001177273170740334</v>
+        <v>5.097232974257787e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0002545129758034936</v>
+        <v>-0.0003028849475493889</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0007648809160127702</v>
+        <v>-0.000249092748202302</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.726122926335675e-05</v>
+        <v>2.033176853911134e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0.0002689406133919947</v>
+        <v>0.0001202537731000664</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0.0001747025055117424</v>
+        <v>-7.7914880272576e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>8.942332185435942e-05</v>
+        <v>0.0002708840411854352</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0002733886601631452</v>
+        <v>0.0001573541624545526</v>
       </c>
       <c r="ER3" t="n">
-        <v>7.16740480616318e-06</v>
+        <v>3.953813347058909e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>1.506213286286196e-05</v>
+        <v>-1.098624037095819e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0005946917475859925</v>
+        <v>8.713190747158267e-06</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.00107681668888841</v>
+        <v>-0.0002613232588572012</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0.0003401330321655293</v>
+        <v>-4.103648882637699e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.000806347475117274</v>
+        <v>-8.519727055934623e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0007687586657542523</v>
+        <v>9.652510013225981e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0006807564697391078</v>
+        <v>-0.0001781169726041143</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003283335938549401</v>
+        <v>0.002732213947633659</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001811295436179233</v>
+        <v>0.0008520416475487191</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001496637653871389</v>
+        <v>0.0008566417252068389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001710790735741494</v>
+        <v>0.002363631421223943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001533400849820104</v>
+        <v>0.001052683745851003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00164830738998129</v>
+        <v>0.003718996457639726</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001717110639029727</v>
+        <v>0.001810012373014233</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003377180459175469</v>
+        <v>0.002826240405351164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002171064578280118</v>
+        <v>0.00165476450566495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007688117325232008</v>
+        <v>0.0004859402192038116</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009056239169112674</v>
+        <v>0.0004280345511455688</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001899535932109378</v>
+        <v>0.001183813807166833</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004148957568898553</v>
+        <v>0.004345218535963623</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001443609922507669</v>
+        <v>0.002691270305145671</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001317005812128864</v>
+        <v>0.001560005772439833</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007672536222628474</v>
+        <v>0.008738864273429845</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002185935110907525</v>
+        <v>0.00176378561372609</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004128490096584296</v>
+        <v>0.004589606843921631</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000549148070339468</v>
+        <v>0.00101160289080326</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001262465657581283</v>
+        <v>0.001558798228448246</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003657979153564788</v>
+        <v>0.001448674785951635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001400632153755042</v>
+        <v>0.002422927344939544</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005212299047447071</v>
+        <v>0.005702214477693689</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001620194311728247</v>
+        <v>0.001359803560414814</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006893957529317149</v>
+        <v>0.004177040462232626</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.006522154185660048</v>
+        <v>0.005714562648961998</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008931877880392686</v>
+        <v>0.0006898881753059951</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005039593869853189</v>
+        <v>0.002280690848475411</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01007113670578645</v>
+        <v>0.004523756140822515</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.007066722581415512</v>
+        <v>0.004922535646301828</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002974896453499548</v>
+        <v>0.002162609833243223</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001498293342614956</v>
+        <v>0.001562141748597187</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001213080216048148</v>
+        <v>0.002059292254535169</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001738275070185188</v>
+        <v>0.00188466522697916</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004000344371131153</v>
+        <v>0.005919494641461092</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.008341513406063093</v>
+        <v>0.008336043016883097</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001525660916141665</v>
+        <v>0.001867073867384435</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005677763829152344</v>
+        <v>0.004897511482922765</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0018375382365101</v>
+        <v>0.001924816487972409</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005999044960843839</v>
+        <v>0.003069841438578789</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001075199579533702</v>
+        <v>0.001501626243123403</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.009532844248465702</v>
+        <v>0.006090515492324968</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.007575574077388562</v>
+        <v>0.005898963038121899</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003616166532261089</v>
+        <v>0.001581924435681154</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002462615399642524</v>
+        <v>0.002512501501549041</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001786787749869567</v>
+        <v>0.002028724131932526</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001049823249364986</v>
+        <v>0.001271274831756544</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001718146141029217</v>
+        <v>0.002166617417355899</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0003651900639672608</v>
+        <v>0.0006812860536941639</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003593111905372597</v>
+        <v>0.002757077871299796</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001418429173526492</v>
+        <v>0.002318355295115713</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004768316686301882</v>
+        <v>0.004388946950629354</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.007177624943970186</v>
+        <v>0.006372839679420612</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0008773847091455714</v>
+        <v>0.0006641060828735918</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0007142980364706823</v>
+        <v>0.0007936036231351278</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.003742547939595375</v>
+        <v>0.001903640544923392</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.003229122205813058</v>
+        <v>0.005443885476643866</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.006413103965948222</v>
+        <v>0.003981329504199556</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0007604125014590697</v>
+        <v>0.001482146139371021</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.01274482575504364</v>
+        <v>0.01083502588286039</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001281653323443718</v>
+        <v>0.002301415363936449</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003154477300576811</v>
+        <v>0.002870944497707072</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0008654570804031124</v>
+        <v>0.0009781532030688038</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002055382206935023</v>
+        <v>0.002294725532577143</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003575859247181371</v>
+        <v>0.003446255896624896</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.003095513663043844</v>
+        <v>0.001257766879297502</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00147611412828138</v>
+        <v>0.001652072034562468</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003934320421528401</v>
+        <v>0.003455877999266222</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001783209873789449</v>
+        <v>0.003342106130470311</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001673313459155276</v>
+        <v>0.001206433569920375</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.00266227501212364</v>
+        <v>0.003738390967745548</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001551191290560144</v>
+        <v>0.001401940557307336</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.000170543295943953</v>
+        <v>0.0001261998165198285</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.00124391010432553</v>
+        <v>0.002260972853724242</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001843003939954622</v>
+        <v>0.001496715849345798</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001753190955684</v>
+        <v>0.002942586713006829</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001302764623428787</v>
+        <v>0.001531158963997761</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001732552135317733</v>
+        <v>0.00338475413792843</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002930592579344913</v>
+        <v>0.002434400843643796</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001560871656769924</v>
+        <v>0.002434791705983391</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.003151739610354481</v>
+        <v>0.0009001519243816673</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001306766680741538</v>
+        <v>0.001481423550060563</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.00149392197938662</v>
+        <v>0.00337423736060373</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001546848389788207</v>
+        <v>0.001212849687354782</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001285620307341696</v>
+        <v>0.002241867510597425</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001418542069177243</v>
+        <v>3.996078669207995e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001225471362680515</v>
+        <v>0.001212710454935062</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.007415244810176721</v>
+        <v>0.004031123021326581</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0007768868420604334</v>
+        <v>0.001212755674109492</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.00141942248505463</v>
+        <v>0.001430555901152633</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001296863214173047</v>
+        <v>0.001974518626722334</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0003648134756991226</v>
+        <v>0.0005193563395891</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002520431220669577</v>
+        <v>0.001962194956380274</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.006991189862234554</v>
+        <v>0.005685875814496266</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.007089010489766905</v>
+        <v>0.00752011203871559</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.00281516119816042</v>
+        <v>0.003082770168140826</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002880446975278929</v>
+        <v>0.0003032009654433682</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002695975022675729</v>
+        <v>0.0002095914009983935</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.003019643261280684</v>
+        <v>0.002862853536210653</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.006445372198582504</v>
+        <v>0.003047214810373322</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0006195012312610648</v>
+        <v>0.0004565853087122973</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0007468851942340923</v>
+        <v>0.0008382698418578994</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001701565252946805</v>
+        <v>0.002181217847804795</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.006492340537323786</v>
+        <v>0.002991919580093844</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004860820313055729</v>
+        <v>0.0002637525487504099</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0008152610512453236</v>
+        <v>0.001039448856836841</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.006797977839444943</v>
+        <v>0.003103968713287132</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001415686261318808</v>
+        <v>0.001159485697828886</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.005738208173265274</v>
+        <v>0.00295601631037967</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001234093492721116</v>
+        <v>0.001946969472381509</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.004070936906539548</v>
+        <v>0.00134868994641813</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001990409474470654</v>
+        <v>0.004971032437686334</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001386208913308743</v>
+        <v>0.0002103568312620911</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0010686640502657</v>
+        <v>0.0009576294151243213</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002068309385354025</v>
+        <v>0.003087680862974807</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004659690059658314</v>
+        <v>0.002238554847259373</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.003191008044376762</v>
+        <v>0.004206925697001746</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.00035051692991183</v>
+        <v>0.0001179553662660688</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.000221657576754682</v>
+        <v>0.0002204559866778165</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001660477815931542</v>
+        <v>0.0002097084283266341</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003817021418942149</v>
+        <v>0.002465443180297852</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.00556202178311264</v>
+        <v>0.00338957044308834</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0004158359014973001</v>
+        <v>0.0006644854087688463</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0008172797993354365</v>
+        <v>0.001308608285478854</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.00315802603028899</v>
+        <v>0.003618468192003579</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003997997061861058</v>
+        <v>0.0002977776800533134</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002655311079309693</v>
+        <v>0.004656729340227994</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003460700507846304</v>
+        <v>0.001898630686705352</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001196730170013092</v>
+        <v>0.001181280165489706</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.00128286721725024</v>
+        <v>0.0006559180084556814</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.000143067434945733</v>
+        <v>0.0001353098780287133</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001093396196171234</v>
+        <v>0.000592437027116996</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0009948561555180439</v>
+        <v>0.0006533256457790083</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0007651178303097297</v>
+        <v>0.000637983797096364</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001713325810346574</v>
+        <v>0.001299551586314105</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001364342819148883</v>
+        <v>0.001423760855880253</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001848525255287172</v>
+        <v>0.0008058067812917527</v>
       </c>
       <c r="EL4" t="n">
-        <v>5.739599109870432e-05</v>
+        <v>0.0001876581566330879</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0004068122012100307</v>
+        <v>0.0004055454900919593</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0002763898408499172</v>
+        <v>0.0004272602686992837</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0004449325131071415</v>
+        <v>0.0004598556104981607</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0006373158812352474</v>
+        <v>0.001632161853436083</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0001418593733251286</v>
+        <v>0.0001065320162270655</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001941524620692173</v>
+        <v>0.0001774790898868931</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001255818424877695</v>
+        <v>0.001112639274426933</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001939732276486038</v>
+        <v>0.001263406376865064</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0006767977705881005</v>
+        <v>0.0005106275381283092</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001217518247294961</v>
+        <v>0.0008162623778981393</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0007915309370771912</v>
+        <v>0.00107019059161493</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001111905025831922</v>
+        <v>0.0006383143800200446</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007029339853300787</v>
+        <v>-0.006540342298288482</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.004491374182034458</v>
+        <v>-0.0009474327628361534</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.004570923031554164</v>
+        <v>-0.001528117359413172</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004322084073416244</v>
+        <v>-0.005621653777513447</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.003650546021840895</v>
+        <v>-0.002028081123244862</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001769389560601653</v>
+        <v>-0.001598245064243142</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.003390838786436601</v>
+        <v>-0.003484107579462059</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005301065975223229</v>
+        <v>-0.002496099843993704</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.003728606356968267</v>
+        <v>-0.00278117359413198</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001828369212621705</v>
+        <v>-0.0005022156573116666</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001975818342671831</v>
+        <v>-0.0009401441554371282</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.005413444378346166</v>
+        <v>-0.002647233789411119</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.007113884555382244</v>
+        <v>-0.007574417919245457</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.004848304580606722</v>
+        <v>-0.007059902200488966</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0005806845965770524</v>
+        <v>-0.002839313572542856</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.007574417919245524</v>
+        <v>-0.01158267020335981</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004274570982839354</v>
+        <v>-0.002839313572542845</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01002444987775065</v>
+        <v>-0.01191931540342294</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0005616224648986367</v>
+        <v>-0.00071762870514811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.001253056234718852</v>
+        <v>-0.001284863679097425</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.007946210268948695</v>
+        <v>-0.003399596658023652</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003331350386674548</v>
+        <v>-0.003242117787031584</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.001427721594289077</v>
+        <v>-0.008358120166567562</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.00503256364712853</v>
+        <v>-0.003433984606275897</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.006481207457827787</v>
+        <v>-0.004971885173128176</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.005544087289885036</v>
+        <v>-0.008001189767995276</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.002160402485942647</v>
+        <v>-0.001219512195122019</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003255401006214909</v>
+        <v>-0.003640130216040294</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01527531083481354</v>
+        <v>-0.002558001189768055</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.003373779224622708</v>
+        <v>-0.001629583202757701</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.00386089006778666</v>
+        <v>-0.001284863679097437</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.003244929797191898</v>
+        <v>-0.002534630120836978</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002776911076443067</v>
+        <v>-0.002433697347893859</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.003775351014040573</v>
+        <v>-0.002121684867394635</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.005578188655593863</v>
+        <v>-0.006298965841428972</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.000265878877400294</v>
+        <v>0.001802067946824271</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002379535990481796</v>
+        <v>-0.003063652587745436</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002983751846381077</v>
+        <v>-0.004105296145408921</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005062166962699855</v>
+        <v>-0.004187555293423728</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.007151589242053846</v>
+        <v>-0.008328375966686541</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.00278117359413208</v>
+        <v>-0.002169926650366716</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.004217603911980494</v>
+        <v>-0.006706361642118431</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001843849034860345</v>
+        <v>0.001894051494524962</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003931357254290202</v>
+        <v>-0.004055654233274119</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.005990220048899808</v>
+        <v>-0.003837753510140362</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001716068642745716</v>
+        <v>-0.001778471138845494</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.003123140987507378</v>
+        <v>-0.00184087363494535</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.002714508580343234</v>
+        <v>-0.002139364303178437</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0005022156573116666</v>
+        <v>-0.0006864274570982154</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.002842298288508615</v>
+        <v>-0.001833740831295794</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.003056234718826467</v>
+        <v>-0.003931357254290113</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.002536674816625961</v>
+        <v>-0.002456348031962174</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01188439988204076</v>
+        <v>-0.001344743276283578</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001754907792980342</v>
+        <v>-0.001528861154446126</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001060842433697362</v>
+        <v>-0.001338488994646092</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.003509815585960685</v>
+        <v>-0.00286051312297253</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.006677067082683341</v>
+        <v>-0.008985959438377478</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01873471882640593</v>
+        <v>-0.01103300733496329</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001368233194527035</v>
+        <v>-0.003004164187983394</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003300913645741266</v>
+        <v>-0.001654357459379607</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.00223105134474334</v>
+        <v>-0.001925427872860608</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.006271450858034333</v>
+        <v>-0.007059902200488988</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001041046995835759</v>
+        <v>-0.001843849034860279</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.005592909535452373</v>
+        <v>-0.003242117787031573</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.006926677067082709</v>
+        <v>-0.00611544461778466</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.004273504273504314</v>
+        <v>-0.001798879386611563</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.003494539781591277</v>
+        <v>-0.003681747269890756</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.003077833678603181</v>
+        <v>-0.003911980440097762</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.001803178484107615</v>
+        <v>-0.002914446881855193</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.003063652587745336</v>
+        <v>-0.001219512195121997</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002620904836193472</v>
+        <v>-0.003715718077263286</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004452963727514058</v>
+        <v>-0.00426198683798179</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0003255401006214798</v>
+        <v>-2.954209748892156e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.002231051344743307</v>
+        <v>-0.005603066941905</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.003656738425243333</v>
+        <v>-0.00194296458790344</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001562960778531486</v>
+        <v>-0.005121373593842538</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.003137951450562515</v>
+        <v>-0.003948605452836063</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.00233362143474497</v>
+        <v>-0.004010616337363571</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.007018578590386381</v>
+        <v>-0.004511943379534001</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.003025672371638211</v>
+        <v>-0.002139364303178448</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.009147424511545344</v>
+        <v>-0.0018096723868954</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.003007962253022756</v>
+        <v>-0.002121684867394647</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.002901716068642779</v>
+        <v>-0.004069595989383612</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.004155614500442129</v>
+        <v>-0.0018096723868954</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.001152405646787602</v>
+        <v>-0.00112324492979714</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0002947244326555465</v>
+        <v>-3.133813851456946e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.001915708812260575</v>
+        <v>-0.002507051081165734</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.02415630550621675</v>
+        <v>-0.01284783895796329</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0002960331557133933</v>
+        <v>-0.00142053862089383</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.00121002592912699</v>
+        <v>-0.00246876859012497</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.00198283515833092</v>
+        <v>-0.003758508434448104</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0008923259964306651</v>
+        <v>-0.001589242053789686</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.002260559190957712</v>
+        <v>-0.002256345973049168</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.02119597394908234</v>
+        <v>-0.01805802249851984</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.02184724689165188</v>
+        <v>-0.02294256956779158</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.00751924215512142</v>
+        <v>-0.009029011249259911</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0003432137285491965</v>
+        <v>-0.0005640864932622613</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0006487761722206553</v>
+        <v>-0.0004126142057176207</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.00793276319669719</v>
+        <v>-0.007313476850486533</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.01986382474837186</v>
+        <v>-0.009532267613972755</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0005305039787798727</v>
+        <v>-0.001283618581907031</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.001308744794764971</v>
+        <v>-0.001243339253996445</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.0005920663114269309</v>
+        <v>-0.0042616158626813</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01974541148608647</v>
+        <v>-0.00813919197876728</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0005327483547477363</v>
+        <v>-0.0004368174726988361</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.0002654084340902974</v>
+        <v>-0.001487209994051209</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.02110716400236829</v>
+        <v>-0.009177027827116635</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.002506112469437694</v>
+        <v>-0.001444149720011745</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01696269982238014</v>
+        <v>-0.008209399167162457</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.001815038893690535</v>
+        <v>-0.002679343128781364</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.01173003241968761</v>
+        <v>-0.001410216233155715</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.004185086943707672</v>
+        <v>-0.01541408782788089</v>
       </c>
       <c r="DL5" t="n">
-        <v>-8.923259964304098e-05</v>
+        <v>-0.0004992199687986698</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.001857859038631737</v>
+        <v>-0.002004126142057128</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.004729327781082648</v>
+        <v>-0.007166027720436396</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01400236826524575</v>
+        <v>-0.004511943379534001</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.009058614564831291</v>
+        <v>-0.012760261748959</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0003255401006214798</v>
+        <v>-0.0001769389560601242</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0004278728606357252</v>
+        <v>-0.0001768346595932613</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0003538779121203817</v>
+        <v>-0.0006267627702914002</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.01169330965068093</v>
+        <v>-0.005532421177870372</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.01752516281823567</v>
+        <v>-0.007270448135380714</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0008736349453978498</v>
+        <v>-0.000535395597858468</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.00220107079119567</v>
+        <v>-0.002947244326554621</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.006098283007696903</v>
+        <v>-0.009071980963712123</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0007138607971445054</v>
+        <v>-0.0004387339392039835</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.008104921898025374</v>
+        <v>-0.01414677276746237</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.01089402013025462</v>
+        <v>-0.003686228251253254</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.001504230648699478</v>
+        <v>-0.002182247124741921</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.003369734789391587</v>
+        <v>-0.000236756436815655</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0.0002379535990482351</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.001427721594289066</v>
+        <v>-0.0002663509914176187</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.002446212791040381</v>
+        <v>-0.001915708812260497</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.001840873634945406</v>
+        <v>-0.0007733491969066586</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.00462717359269087</v>
+        <v>-0.002319022250078307</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002714508580343211</v>
+        <v>-0.002444374804136573</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.003654582964927822</v>
+        <v>-0.001503094606542821</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0.0002664298401421128</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.001219512195121919</v>
+        <v>-0.0004368174726988472</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0008112324492980272</v>
+        <v>-0.001222187402068287</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0005928237129485647</v>
+        <v>-0.0003831417624520661</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.001243339253996489</v>
+        <v>-0.001974653698791584</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0002820432466311251</v>
+        <v>-8.841732979660843e-05</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0003536693191865892</v>
+        <v>-0.000407395800689403</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.002498512790005902</v>
+        <v>-0.001092043681747201</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.004656646035956424</v>
+        <v>-0.002287684111563726</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.001887348864641769</v>
+        <v>-0.00141467727674619</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.003182527301092053</v>
+        <v>-0.001338488994646092</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.002028081123244929</v>
+        <v>-0.001405867970660113</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.003331350386674548</v>
+        <v>-0.001427721594289177</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001309322509723668</v>
+        <v>-0.0001701270743566713</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0004341911720663532</v>
+        <v>-0.000207937642551706</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.001448637311624773</v>
+        <v>-0.001337221035858962</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0006236402110094547</v>
+        <v>-0.001293398797158979</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001226569051532733</v>
+        <v>-0.0001652202602210995</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0004659962064764599</v>
+        <v>-0.0003549659227747942</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001484059275604696</v>
+        <v>-0.00096925889733393</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.003684736861718243</v>
+        <v>-0.001006704626458366</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.00231524255158507</v>
+        <v>-0.001119019170983332</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0008105164944666011</v>
+        <v>0.0001173421967792271</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0004569621790627476</v>
+        <v>-0.0001400268235877716</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.002854620395750363</v>
+        <v>-0.0007521024506333657</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002962777861132274</v>
+        <v>-0.003585700308317821</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001955585328208917</v>
+        <v>-0.001808380290246556</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0004195769377585645</v>
+        <v>2.950297109969302e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0007115769983813718</v>
+        <v>0.0002572319548107383</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001670979470609937</v>
+        <v>-0.0009276620357172694</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002708085726435963</v>
+        <v>-0.001370285444843297</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0004009352460089766</v>
+        <v>-0.0002012787814717559</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0002514615078420018</v>
+        <v>2.34009360374765e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.002640747009190756</v>
+        <v>-0.00157837890045272</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001448536874681552</v>
+        <v>-0.002193370747410828</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0009234841303764341</v>
+        <v>-0.001620874215205387</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0003687273680831771</v>
+        <v>-0.0003708283162786819</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0006145911783047548</v>
+        <v>-0.0007111567192489509</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001849292462830876</v>
+        <v>0.001305281003749034</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.001269432816652116</v>
+        <v>-0.0005027716220581041</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0004240243523671666</v>
+        <v>-0.002930645030566884</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.003436350937183569</v>
+        <v>0.0003572284142044746</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.000624343115689921</v>
+        <v>0.003673253295063347</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0009744242360767957</v>
+        <v>-0.0002192731387415825</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001284402112090194</v>
+        <v>-0.0009659756810577152</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0008486039733760387</v>
+        <v>-0.0007026813273368321</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0004429224996637033</v>
+        <v>0.0002957881746804281</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002651639522480134</v>
+        <v>-0.002786421801699609</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.006010002976910181</v>
+        <v>0.007619246780093202</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.001283907081651434</v>
+        <v>-0.0004114081698514654</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0003985345875759105</v>
+        <v>0.0002508334033916787</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001551145550799235</v>
+        <v>-0.001665692204952812</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003126558099624183</v>
+        <v>-0.002234282294535531</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001631351902043796</v>
+        <v>-0.001026112954630507</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0008825238730977736</v>
+        <v>0.0001523511756197082</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003887463679930733</v>
+        <v>0.002870497345452821</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0008921195082822603</v>
+        <v>-0.0009554554920329639</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.001887137086055549</v>
+        <v>-0.002153474176399453</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0009897991350303504</v>
+        <v>-0.0008913507120806268</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0007544587834826227</v>
+        <v>-0.0001403380773506408</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001297537375597868</v>
+        <v>-0.000611341560977674</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001847974481276049</v>
+        <v>-0.0005490548641420761</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.001032191278465805</v>
+        <v>-0.0007102299676121555</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0007308270957644247</v>
+        <v>-0.0009441169513132979</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0003324399546438094</v>
+        <v>-6.607680037538645e-05</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0006443373433058647</v>
+        <v>-0.0007740173203932693</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0006189259709220851</v>
+        <v>-0.0003937064436393967</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0007482938029571146</v>
+        <v>-0.0004414440274137704</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001953832090175444</v>
+        <v>0.000299911077453352</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.002065192651145539</v>
+        <v>-0.0007904818102463684</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001353290652431696</v>
+        <v>-0.001685515859776793</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.000314665887123916</v>
+        <v>-0.0009766981521210139</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0006106862089651692</v>
+        <v>-5.124096953957601e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.001562243740321656</v>
+        <v>-0.0009744041729706887</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001657224716287442</v>
+        <v>-0.001161849097208406</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0001920542427192113</v>
+        <v>-0.001017085415763583</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002864010763698804</v>
+        <v>-0.001674968685637074</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001625457961525331</v>
+        <v>-0.0008406952629407521</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.003671019456915228</v>
+        <v>-0.00105945463395796</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001507195514661902</v>
+        <v>0.0002344387092432926</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001437401316277323</v>
+        <v>-0.001889862982583757</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001013661624253592</v>
+        <v>-0.0007609726862979975</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0001989277327044348</v>
+        <v>-0.0005184730284336441</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0001474274016195848</v>
+        <v>-0.000452003309083579</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001900158294501644</v>
+        <v>-0.001722889855510959</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>7.372456502507951e-06</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001697595993727385</v>
+        <v>-0.00104629241449195</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001353518101856871</v>
+        <v>-0.0008360899723521887</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001162985199490862</v>
+        <v>-0.001323654178253103</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.001376251125794103</v>
+        <v>-0.0002285548429499129</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0006033665990640286</v>
+        <v>-0.0003287547763341753</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001462720026901987</v>
+        <v>-0.0002094034042509657</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.00218102103080719</v>
+        <v>-0.001306638676182154</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001166888492113019</v>
+        <v>-0.0008826174935075426</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0007142173327382123</v>
+        <v>-0.0009455190295949544</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0009849642444872768</v>
+        <v>-0.0009373093810397055</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001914139829651904</v>
+        <v>-0.001439838871119492</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0008160280434206136</v>
+        <v>-7.422122188192881e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-4.584352078241816e-05</v>
+        <v>-2.160760587727462e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0002691527173127401</v>
+        <v>-0.0002519057461550234</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.004237180856070666</v>
+        <v>-0.0009495586467815509</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0004187808527068598</v>
+        <v>0.0003189244327444718</v>
       </c>
       <c r="CN6" t="n">
-        <v>8.104921898024198e-05</v>
+        <v>-0.0003037045197742644</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0002631758452967259</v>
+        <v>0.0001569412351668464</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.0002862788668849869</v>
+        <v>-0.0001235042415537319</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0003344385774799813</v>
+        <v>0.0001039463084506254</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002065152423499328</v>
+        <v>-0.002083440959030158</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.00338414815956852</v>
+        <v>-0.001540349099434707</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.0006990386658096814</v>
+        <v>-0.00200986802113367</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0002673946453410236</v>
+        <v>-0.0003291841331354461</v>
       </c>
       <c r="CV6" t="n">
-        <v>-7.758833248456832e-05</v>
+        <v>-8.579198525189569e-05</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.001268809721803635</v>
+        <v>-0.002068741583690731</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.002254925920353495</v>
+        <v>-0.002219086040742644</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-7.422833465146329e-05</v>
+        <v>-0.0007373345708618112</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.0004495766546905339</v>
+        <v>-0.0001412344238368668</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0004745694118007765</v>
+        <v>-8.629887292943561e-06</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.001456301253191092</v>
+        <v>-0.001176591891261808</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0003107625355016464</v>
+        <v>-0.0002730352644637224</v>
       </c>
       <c r="DE6" t="n">
-        <v>-8.629887293001847e-06</v>
+        <v>-7.386835800057002e-05</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0007173794349756901</v>
+        <v>-0.001822197553246943</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0006335697871158812</v>
+        <v>-0.0007677436885065309</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.005273472962952122</v>
+        <v>-0.001296220698718217</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0005593778092388618</v>
+        <v>-0.0009443551681683676</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0001329394387001581</v>
+        <v>-6.983509540102738e-05</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.00168233597664165</v>
+        <v>-0.0008253948980095516</v>
       </c>
       <c r="DL6" t="n">
-        <v>-4.439183190292906e-05</v>
+        <v>-0.0001182997727240453</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0005804173732972623</v>
+        <v>-0.0004255181443213074</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.001843738318213972</v>
+        <v>-0.003744190894350383</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.00108160706336323</v>
+        <v>-0.001582826477442923</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.005022797220189973</v>
+        <v>-0.002775190396981453</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0001850871195621745</v>
+        <v>-2.220248667851033e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>-6.631299734749795e-05</v>
+        <v>-3.088912825815749e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>-7.962009493277522e-05</v>
+        <v>-2.21173695075072e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.001510688013727457</v>
+        <v>-0.002516187643143306</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.002826860802417075</v>
+        <v>-0.002608840925207209</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0002542574567763439</v>
+        <v>-0.0001400114882557896</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0007460458735815273</v>
+        <v>-0.0002171739932515626</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.00130060133245144</v>
+        <v>-0.004883159812945039</v>
       </c>
       <c r="DZ6" t="n">
-        <v>7.654930526077575e-05</v>
+        <v>-0.0001572498355020741</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.001295523099213902</v>
+        <v>-0.001124619901298962</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.00214710802104773</v>
+        <v>-0.002751868334058388</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0007326294945744577</v>
+        <v>-0.001671519102965818</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.001082987930602525</v>
+        <v>0.0002782387157555771</v>
       </c>
       <c r="EE6" t="n">
-        <v>2.775557561562892e-18</v>
+        <v>-5.400440736730017e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0004511858148972009</v>
+        <v>7.385524372263697e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.000573173740860905</v>
+        <v>-0.0006455636780411972</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.001101760165165036</v>
+        <v>-0.0001473970434393901</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001597387044995263</v>
+        <v>-0.0003192448927407693</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0009791573773332146</v>
+        <v>-0.001640886325108126</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.001987849993473262</v>
+        <v>-0.0008446174032779835</v>
       </c>
       <c r="EL6" t="n">
-        <v>2.897571669365773e-05</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0004279713182197248</v>
+        <v>-4.420866489829034e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0002727419950972476</v>
+        <v>-4.461629982154824e-05</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0001162103314951812</v>
+        <v>-7.424867207020402e-06</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0007272623533165518</v>
+        <v>-0.0003819527184876909</v>
       </c>
       <c r="ER6" t="n">
+        <v>-2.220248667851033e-05</v>
+      </c>
+      <c r="ES6" t="n">
         <v>0</v>
       </c>
-      <c r="ES6" t="n">
-        <v>-7.020280811233793e-05</v>
-      </c>
       <c r="ET6" t="n">
-        <v>-0.001572071664074753</v>
+        <v>-0.0005310049493269159</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.002288567100442332</v>
+        <v>-0.0008550454377725225</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0005266458110535638</v>
+        <v>-2.340093603744597e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.001343631294020975</v>
+        <v>-0.0005307386458302893</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.001354589005865911</v>
+        <v>-0.000556004308646843</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0008168459953318525</v>
+        <v>-0.000459522273447821</v>
       </c>
     </row>
     <row r="7">
@@ -3552,442 +3552,442 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001919372152352994</v>
+        <v>0.0005972309149372469</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003104152283450345</v>
+        <v>0.0002930935553522696</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001149506057199046</v>
+        <v>-0.0006422424991892549</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0002366777511460749</v>
+        <v>-0.0001108917919934616</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002651475080548471</v>
+        <v>0.0001623769932312946</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000489384977448487</v>
+        <v>0.0008280426083689008</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004872105007169725</v>
+        <v>-1.300741052068265e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0006900851522516016</v>
+        <v>-0.0007601322722514403</v>
       </c>
       <c r="J7" t="n">
-        <v>6.137553597705962e-05</v>
+        <v>-0.0004814387109236041</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0003661794365337978</v>
+        <v>0.000306442093372844</v>
       </c>
       <c r="L7" t="n">
-        <v>5.762028233938787e-05</v>
+        <v>7.239133108383756e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.001164997359669612</v>
+        <v>-1.515414697299543e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0007682016765476363</v>
+        <v>0.001581527077639611</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001491411168320311</v>
+        <v>-0.0008743032143737395</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.896226927561976e-05</v>
+        <v>0.0002190038840495845</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00273065770152725</v>
+        <v>0.004149757306974239</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0006816913685582903</v>
+        <v>-0.0007361962024904412</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0006508356055207054</v>
+        <v>0.0005901736808024971</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001079486618578096</v>
+        <v>0.0005607426185025244</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002325080415144287</v>
+        <v>0.0004487530570878917</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004139041075230832</v>
+        <v>-0.0004743359226661803</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0003625056615623124</v>
+        <v>-0.0002134312846664321</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.489471801641387e-05</v>
+        <v>-2.928074009443394e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>5.971286768063355e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001600907209644142</v>
+        <v>0.001660648405256798</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001825196025879849</v>
+        <v>0.001940021442913531</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0006812549589017669</v>
+        <v>-0.000136000187798152</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0007729747392142994</v>
+        <v>-0.0001404056162245981</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.004602003300914093</v>
+        <v>0.003102600508514736</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.003718414027035833</v>
+        <v>0.006891399690195865</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001241423120720281</v>
+        <v>0.00158218571292395</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0005016504195784977</v>
+        <v>-8.552951038901527e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0002368002416626047</v>
+        <v>-0.0004879429511410294</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.000351838857599307</v>
+        <v>0.001105713349029908</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.0002860899882889845</v>
+        <v>0.00149368569359013</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01205912979795472</v>
+        <v>0.01226312500775899</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0002388874041597433</v>
+        <v>2.75461424972534e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001967463207195636</v>
+        <v>0.001893694225299214</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0008702380999024594</v>
+        <v>-0.0001015674504131703</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.001132002034019924</v>
+        <v>8.447841606429307e-05</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.001031118604909936</v>
+        <v>-0.0006801764132711496</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0002661411629654497</v>
+        <v>0.000906061548085435</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.005537982485713871</v>
+        <v>0.005134831325757499</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002046513476191891</v>
+        <v>-0.0004346465571791192</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0007411285540186217</v>
+        <v>0.0004192109595989812</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.000253489299289239</v>
+        <v>-0.000408465670610314</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0005318472034803346</v>
+        <v>0.0002661848370144826</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.000122658492519806</v>
+        <v>-0.0002803364821395427</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.354636280247126e-05</v>
+        <v>5.598741290013251e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001739696836145172</v>
+        <v>0.0009878136945822903</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002363642300995172</v>
+        <v>-0.0001596323965817326</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001966906379186545</v>
+        <v>0.0008705771250425431</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001732747858280598</v>
+        <v>-0.0001455398823442866</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0002811396708041536</v>
+        <v>-0.0001748437830222993</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.000435445920981875</v>
+        <v>-0.0002654609520600259</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.001044118667141558</v>
+        <v>0.0007420029580082865</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001305363571332724</v>
+        <v>0.000341329956120906</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0001033973412112088</v>
+        <v>1.212614352585949e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>-4.56063186347444e-05</v>
+        <v>0.000598555519128946</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00373989201621851</v>
+        <v>0.002190247434403841</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.001064249909183634</v>
+        <v>0.0005178505847352077</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0007071862953296592</v>
+        <v>-0.0005801582830588237</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001768259682210005</v>
+        <v>-9.111501830824653e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0008870497813631195</v>
+        <v>3.885780586188048e-17</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.000240505684895942</v>
+        <v>0.0004445925816552288</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.003069327347757883</v>
+        <v>-0.0001910259292646599</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0004979962331149613</v>
+        <v>0.0003800524647654347</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0002663841333805372</v>
+        <v>-0.001003038230155811</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0002624534465164085</v>
+        <v>-3.416228603109217e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0004700036324862322</v>
+        <v>-8.467821749050807e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0002144465551674968</v>
+        <v>0.0002643899578368969</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.001230493517806647</v>
+        <v>-0.00158076990969197</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.665334536937735e-17</v>
+        <v>4.440059287232345e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.00105187867324143</v>
+        <v>-0.0002068991637574846</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0003440074138778893</v>
+        <v>7.281670577172217e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0002090178087355953</v>
+        <v>0.0002334617985158549</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.0002409279035584244</v>
+        <v>0.0001462465748061359</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0004129621070981415</v>
+        <v>0.001220430426412495</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0005643831732835613</v>
+        <v>0.0001041046995835793</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.0007140046767414643</v>
+        <v>-0.0006961352527415422</v>
       </c>
       <c r="CE7" t="n">
-        <v>-9.072350471437399e-05</v>
+        <v>-0.00032605912421384</v>
       </c>
       <c r="CF7" t="n">
-        <v>-8.902421000253624e-05</v>
+        <v>-0.0001920542427192084</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0003856270814997898</v>
+        <v>-0.0002028081123244596</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0005525483158348831</v>
+        <v>1.387302823165349e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.000482043302900681</v>
+        <v>0.0003141300973726002</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>9.20064919955943e-05</v>
+        <v>0.0006067672180645467</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.002142692664773355</v>
+        <v>-0.0002543304314866157</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0007082524032901271</v>
+        <v>0.0003560850927141757</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001381306406785554</v>
+        <v>0.0002501846167092203</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0001174364336364753</v>
+        <v>0.0005606729642791575</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0002472140471481976</v>
+        <v>-4.560631863476106e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0005908438061197729</v>
+        <v>0.001429038398588328</v>
       </c>
       <c r="CR7" t="n">
-        <v>3.560698957305044e-05</v>
+        <v>-0.001209658777019818</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0005734694189298117</v>
+        <v>-0.0004905771956448035</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0003599736181550017</v>
+        <v>-0.00076922236264218</v>
       </c>
       <c r="CU7" t="n">
-        <v>-7.83453462864403e-05</v>
+        <v>-1.44050705848886e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.007845089510464e-05</v>
+        <v>6.094544793094347e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0002652690377278</v>
+        <v>-0.0005465834251130841</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.000842081700794095</v>
+        <v>-0.00138461484416712</v>
       </c>
       <c r="CZ7" t="n">
-        <v>8.762597694920715e-05</v>
+        <v>-0.0001972288065787753</v>
       </c>
       <c r="DA7" t="n">
-        <v>5.951591260914823e-05</v>
+        <v>7.280976635647973e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001144597173355594</v>
+        <v>0.0002913923225262516</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.0005801582830588514</v>
+        <v>-0.0007273364360889211</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001044221544142743</v>
+        <v>1.431338100784107e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0005082312947833845</v>
+        <v>0.0002117566224724532</v>
       </c>
       <c r="DF7" t="n">
-        <v>-3.599288647244123e-05</v>
+        <v>-0.001012394518769194</v>
       </c>
       <c r="DG7" t="n">
-        <v>-1.987917912473213e-05</v>
+        <v>-0.000156835815530082</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0006058725107625285</v>
+        <v>-0.00106244511013911</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.0002310952640366071</v>
+        <v>-0.0002362449527877397</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002740933321080497</v>
+        <v>0.0003248593647739772</v>
       </c>
       <c r="DK7" t="n">
-        <v>8.552951038902633e-05</v>
+        <v>-0.0004574582035076602</v>
       </c>
       <c r="DL7" t="n">
-        <v>7.827690105409181e-05</v>
+        <v>-4.46162998215538e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0002556989523028852</v>
+        <v>-1.452617641478079e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0004217513624396596</v>
+        <v>0.0005754440130236238</v>
       </c>
       <c r="DO7" t="n">
-        <v>-4.797292782950937e-05</v>
+        <v>-0.0006809967997741473</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.002413117214343757</v>
+        <v>-0.0007185758694715106</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-1.440507058484419e-05</v>
+        <v>2.94724432655602e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.372456502505176e-05</v>
+        <v>4.461629982150938e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>-5.551115123125783e-18</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0004675006696943373</v>
+        <v>-0.0005475194034921749</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.00150903634610321</v>
+        <v>0.0004265829498848961</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
+        <v>-4.68018720748864e-05</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.0003322858672823948</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0.0008497431908397913</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-7.280976635650748e-05</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>-0.0001380145093444196</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>-0.001551617849779841</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0.0005021537234981887</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.0005765662010075612</v>
+      </c>
+      <c r="EE7" t="n">
         <v>0</v>
       </c>
-      <c r="DX7" t="n">
-        <v>-7.447028279805034e-05</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>4.301240518128635e-05</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>0.0001520114090531377</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>-0.0001960269476958543</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>-0.0009537863125375523</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>-0.0001641994065219144</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>-0.0005679149163720032</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>4.441076519465793e-05</v>
-      </c>
       <c r="EF7" t="n">
-        <v>-0.0001833645929649019</v>
+        <v>0.0003324319949471077</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0003844145758505446</v>
+        <v>-0.0003912695833675761</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0.0001477285503369619</v>
+        <v>-1.566906925728473e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0008331185678192687</v>
+        <v>0.0001494244618892471</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0002453169850396231</v>
+        <v>0.0002472394402391498</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.0003479625806278918</v>
+        <v>-7.633962680171359e-05</v>
       </c>
       <c r="EL7" t="n">
-        <v>4.482327108304985e-05</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0.0002334844562066896</v>
+        <v>1.528117359413383e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0.0001071554874561176</v>
+        <v>4.431314623338234e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-1.528117359415604e-05</v>
+        <v>0.0001458029118670434</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0003640421478928568</v>
+        <v>-7.312328740309848e-05</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0004742838520555625</v>
+        <v>-0.0002071919036831849</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0004544013224528132</v>
+        <v>-2.98190225205941e-05</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>1.477104874446078e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.0006786323915647153</v>
+        <v>-8.008893019904596e-05</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0006748996904941795</v>
+        <v>2.937683817095247e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0004380352182873082</v>
+        <v>-4.284923359494929e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009975508394310828</v>
+        <v>0.002166484920964842</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006944884622765545</v>
+        <v>0.0009962240279032726</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0002094420855485668</v>
+        <v>-9.411511023521563e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004541634501481428</v>
+        <v>0.001258418363686301</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0007392878577932166</v>
+        <v>0.0004277472891937778</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002105901203308757</v>
+        <v>0.003732164829887188</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0007624752878530427</v>
+        <v>0.0009764597480451333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001810427869742587</v>
+        <v>0.001218876202685865</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0008889447729983818</v>
+        <v>0.0009439357897153667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002144982351017954</v>
+        <v>0.0005025884550534821</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003652964773796563</v>
+        <v>0.000333275441149869</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0004619262687923592</v>
+        <v>0.0006131151431319204</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001869465893012709</v>
+        <v>0.002189144612457755</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.001311985027222617</v>
+        <v>0.0009363799607354922</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001521574181676125</v>
+        <v>0.0009349573284713142</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.004941386067162167</v>
+        <v>0.005740836935025773</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0005609238139306555</v>
+        <v>0.0005674316006410273</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001452651364481552</v>
+        <v>0.001450781704309212</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001905766184219837</v>
+        <v>0.001437099206152118</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00098405398439248</v>
+        <v>0.001093406637139635</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001715931268180704</v>
+        <v>0.0004001653468696936</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002750498387463607</v>
+        <v>0.000862232514886585</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001143125650733459</v>
+        <v>0.0012521052566241</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001249267328306353</v>
+        <v>0.0003220676505700404</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003799665527090032</v>
+        <v>0.003282691497889081</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004180002226646634</v>
+        <v>0.006385013284366484</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.0003877730101320504</v>
+        <v>0.0001717277624939451</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.003057321438456528</v>
+        <v>0.0001761546504546796</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01202058326130942</v>
+        <v>0.006414590208967097</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.007694489847855556</v>
+        <v>0.008821367190216461</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002295002306159111</v>
+        <v>0.003649958568960946</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006197956471344108</v>
+        <v>0.0004158517587922239</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0003362529896954403</v>
+        <v>0.001319528772529352</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0007580099760421232</v>
+        <v>0.001831030350489155</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001759284674409273</v>
+        <v>0.006338948629706362</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01960960529436057</v>
+        <v>0.0188420534632909</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001115053797554194</v>
+        <v>0.001240294900979119</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.004161251246952952</v>
+        <v>0.0032353837670381</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.000249230146829485</v>
+        <v>0.000451691070877433</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.938528305219401e-05</v>
+        <v>0.0006432831883006584</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.0003160114509447198</v>
+        <v>0.0008756732793931993</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00122469036692501</v>
+        <v>0.001716987104524134</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01063973593426494</v>
+        <v>0.009658483006307238</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001351531450388788</v>
+        <v>0.0001781312631815968</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001011843067552079</v>
+        <v>0.001578230150209633</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0004971283215452593</v>
+        <v>0.001010479746919865</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.0003106267217332148</v>
+        <v>0.0008172574792507909</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0006660316711046055</v>
+        <v>0.001464503359481983</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0002898151684367606</v>
+        <v>0.000769642400007986</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.00445003314730047</v>
+        <v>0.001438872888772352</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0006731387297947228</v>
+        <v>0.0007926169460845233</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.006125115877642053</v>
+        <v>0.002492279842681025</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.008704970206509871</v>
+        <v>0.005098014659204378</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.359419444108449e-06</v>
+        <v>0.0003571236262318367</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0001974455159907962</v>
+        <v>-5.888380778493184e-06</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001527734252585383</v>
+        <v>0.002581034278950722</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001650642106198719</v>
+        <v>0.004520762001662007</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.000801898546672361</v>
+        <v>0.0007388433382891357</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0002285287688331833</v>
+        <v>0.0009910234640656324</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.008251793735136048</v>
+        <v>0.006467396817078136</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-8.939009245761688e-05</v>
+        <v>0.003172146728384059</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0004863077039012037</v>
+        <v>0.0004795276400017034</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0006972619889710707</v>
+        <v>0.0004060381658684498</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.927819391090884e-05</v>
+        <v>0.0007129190715900153</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001945672026672804</v>
+        <v>0.002064992374025151</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0005862543363924499</v>
+        <v>0.001080469118509589</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0001950174201348714</v>
+        <v>0.0009223726351257401</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002851680515933739</v>
+        <v>0.002268930670814598</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001076446628590133</v>
+        <v>0.0008046954598300432</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001423446023381866</v>
+        <v>0.0003357628010477648</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002264535368121012</v>
+        <v>0.001066801310752555</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.0004171321185411608</v>
+        <v>-0.0006629282162578076</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.397557085189188e-05</v>
+        <v>0.0001917067595338384</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.0003778286872441917</v>
+        <v>0.000997543135913323</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.000423398545137188</v>
+        <v>0.001581828427639812</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001378850983034194</v>
+        <v>0.001695625752436239</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.806885954893261e-05</v>
+        <v>0.0004676730467752133</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0009409754057956299</v>
+        <v>0.002174321919511721</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001055647339160881</v>
+        <v>0.0002967678596277807</v>
       </c>
       <c r="CD8" t="n">
-        <v>-3.889810764864943e-06</v>
+        <v>0.0002369525401736599</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0007915100785413992</v>
+        <v>0.000353721559854131</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0006319355571385771</v>
+        <v>0.0003593495276086905</v>
       </c>
       <c r="CG8" t="n">
-        <v>-9.585509483642785e-05</v>
+        <v>0.00145590558221324</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0001852444164820166</v>
+        <v>0.0006226919908917522</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0003183250618666007</v>
+        <v>0.0006715256020954546</v>
       </c>
       <c r="CJ8" t="n">
-        <v>7.771334695020615e-05</v>
+        <v>2.211736950753218e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0007325443197052917</v>
+        <v>0.0009358252691966189</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.0003971714143821331</v>
+        <v>-6.779276794033895e-05</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001499430092146212</v>
+        <v>0.0007820472643412596</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.00170759314582781</v>
+        <v>0.001104387083180233</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0009886194687211303</v>
+        <v>0.0007346427038293246</v>
       </c>
       <c r="CP8" t="n">
-        <v>5.918034823451102e-05</v>
+        <v>2.230814991074914e-05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00178579053274491</v>
+        <v>0.002814857029826304</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0009543404626821989</v>
+        <v>0.0003574712848476352</v>
       </c>
       <c r="CS8" t="n">
-        <v>8.3791554408158e-06</v>
+        <v>0.001288113842798663</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.969367428302949e-05</v>
+        <v>0.0001520161546253368</v>
       </c>
       <c r="CU8" t="n">
-        <v>5.061604064740544e-05</v>
+        <v>0.0001331754957087788</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0001044790159713011</v>
+        <v>0.0001175938049755465</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0001293798507004229</v>
+        <v>-0.0001233580453702587</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001002673847785174</v>
+        <v>-0.0002820432466311557</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002607384043101235</v>
+        <v>-7.398638650488176e-06</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0002240630074974076</v>
+        <v>0.0002302575736176343</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002558042280405434</v>
+        <v>0.001104115459197275</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0.0001389498026564906</v>
+        <v>0.0001670726598361427</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0001441508994448837</v>
+        <v>8.807732522733702e-05</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.001345928143842529</v>
+        <v>0.001039095875758703</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0006646343783555025</v>
+        <v>-0.0002330429764748648</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0006354611864239218</v>
+        <v>0.0005501114215854697</v>
       </c>
       <c r="DH8" t="n">
-        <v>2.981749733233505e-05</v>
+        <v>0.0004216308195755275</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0001034496126901069</v>
+        <v>0.00120225148051637</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001052352032152615</v>
+        <v>0.0008692599625495124</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001144440880343853</v>
+        <v>0.0001647242530143589</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0001735432388092789</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.000581492784927412</v>
+        <v>0.0004084964012070508</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0.0001090314825301503</v>
+        <v>0.0009752149137914556</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0006382896218807721</v>
+        <v>0.0005497715402616205</v>
       </c>
       <c r="DP8" t="n">
-        <v>-0.0001254358858235965</v>
+        <v>-0.0001671222243642162</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0001040179538215891</v>
+        <v>0.0001087385734198254</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001479400552536703</v>
+        <v>0.0002172906598415986</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>4.461629982152326e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0005944353956220922</v>
+        <v>0.0009470060342756409</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0002214870454973594</v>
+        <v>0.001685781625471849</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001110124333925183</v>
+        <v>0.0005686889431415765</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0002587482809656816</v>
+        <v>0.001154457029284925</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0008842775944332554</v>
+        <v>-1.097934478883068e-06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002892604403646859</v>
+        <v>1.478411661419155e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0002658788774002885</v>
+        <v>0.000634240716399459</v>
       </c>
       <c r="EB8" t="n">
-        <v>-6.64174786825733e-05</v>
+        <v>0.0002359708017517476</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0005503645433173415</v>
+        <v>0.0001899944202273352</v>
       </c>
       <c r="ED8" t="n">
-        <v>-2.971258310627278e-05</v>
+        <v>0.0007499829658401402</v>
       </c>
       <c r="EE8" t="n">
-        <v>8.351019417858763e-05</v>
+        <v>8.10579103525222e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0004302127141265377</v>
+        <v>0.000603695271605939</v>
       </c>
       <c r="EG8" t="n">
-        <v>3.441463494584518e-05</v>
+        <v>-0.0002926294565008925</v>
       </c>
       <c r="EH8" t="n">
-        <v>8.142442234179425e-05</v>
+        <v>4.439183190293738e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001479858872880213</v>
+        <v>0.001041708808672065</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003905753094213676</v>
+        <v>0.0007022612864329674</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.000178313622492085</v>
+        <v>0.000207116077355185</v>
       </c>
       <c r="EL8" t="n">
-        <v>5.941795760721624e-05</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>6.631299734746466e-05</v>
+        <v>0.0001793268849872215</v>
       </c>
       <c r="EN8" t="n">
-        <v>1.468131953726581e-05</v>
+        <v>0.0001231982987517366</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0004535485225876295</v>
+        <v>0.0005424678797827626</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0001249166580801153</v>
+        <v>0.0001109795797573337</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>5.171178488387052e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>9.281896156855817e-05</v>
+        <v>6.482281763178221e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0001967613862288997</v>
+        <v>0.0001364559638398738</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0003476706082365999</v>
+        <v>0.00047167588201944</v>
       </c>
       <c r="EV8" t="n">
-        <v>2.220248667848812e-05</v>
+        <v>0.0002161324227190842</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0002297987375664085</v>
+        <v>0.0004290950305784191</v>
       </c>
       <c r="EX8" t="n">
-        <v>-0.000474216586380255</v>
+        <v>0.0005357330586521824</v>
       </c>
       <c r="EY8" t="n">
-        <v>5.896658415029954e-05</v>
+        <v>0.0002139321493126289</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005426127985844809</v>
+        <v>0.002772043644942546</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002427471876850151</v>
+        <v>0.001651430256561559</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002193669696020084</v>
+        <v>0.0007976366322008821</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001503981126511311</v>
+        <v>0.002575488454706931</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001347539956126587</v>
+        <v>0.001034158570980914</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002855443188578266</v>
+        <v>0.01000592066311428</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001372854914196542</v>
+        <v>0.002536125036862347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004010616337363537</v>
+        <v>0.007225007372456549</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002713063992922382</v>
+        <v>0.002623047450633698</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004736530491414648</v>
+        <v>0.001179593040401117</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005328596802841368</v>
+        <v>0.0005501222493887959</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0005622965374371014</v>
+        <v>0.001209082866411149</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006900654372397452</v>
+        <v>0.004907792980368764</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.267627702915002e-05</v>
+        <v>0.002123267472721979</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003078744819419721</v>
+        <v>0.003033908387864326</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01613380698638244</v>
+        <v>0.01811421772754308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003197158081705109</v>
+        <v>0.003730017761989324</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005396638159834799</v>
+        <v>0.00404010616337368</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001238572692421069</v>
+        <v>0.002241226776762095</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002505157677571446</v>
+        <v>0.004203670811130855</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004276024771453779</v>
+        <v>0.0006487761722206332</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001029641185647412</v>
+        <v>0.005013270421704552</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01604512691946098</v>
+        <v>0.01410216233155754</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0005501222493887292</v>
+        <v>0.001797819039198378</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01924449732302206</v>
+        <v>0.01024274718768501</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01612135633551463</v>
+        <v>0.01158312958435213</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001238572692421069</v>
+        <v>0.000811232449298005</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01145648312611008</v>
+        <v>0.003025672371638155</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01400814791601378</v>
+        <v>0.01104203670811134</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01906603212373594</v>
+        <v>0.01525877453896485</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007045589105979843</v>
+        <v>0.004253420582986256</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.00144500147449127</v>
+        <v>0.003302860513123029</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001562039493073963</v>
+        <v>0.004010616337363648</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.002320047590719854</v>
+        <v>0.00518058022498522</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.008876437629017931</v>
+        <v>0.01241521675022121</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02243810717643372</v>
+        <v>0.02665080309339675</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001930279458369411</v>
+        <v>0.003863167207313545</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01447602131438714</v>
+        <v>0.01326591314693631</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001213376738680061</v>
+        <v>0.00279988211022697</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01410216233155749</v>
+        <v>0.001769389560601653</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0004420866489831865</v>
+        <v>0.002782711663706328</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.02873289708506847</v>
+        <v>0.01474245115452931</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.02694824509220707</v>
+        <v>0.02064247471743006</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.009325044404973327</v>
+        <v>0.0006914433880725546</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002287684111563759</v>
+        <v>0.002947244326554721</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.004588513913558278</v>
+        <v>0.004262877442273527</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0002067946824224509</v>
+        <v>0.002093777646711947</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002723505032563611</v>
+        <v>0.00498378059569452</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0006216696269982003</v>
+        <v>0.0009141846063108749</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.008555358200118369</v>
+        <v>0.007252812314979295</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001591511936339485</v>
+        <v>0.004361921603300967</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01210588935157649</v>
+        <v>0.0134146341463414</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01267102914931594</v>
+        <v>0.01933372992266502</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001629583202757734</v>
+        <v>0.0008557457212714281</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001209082866411038</v>
+        <v>0.001213735938425109</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.009048040082522801</v>
+        <v>0.003569303985722727</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.004715590922487467</v>
+        <v>0.01124330755502672</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001509322284699588</v>
+        <v>0.003627248599233301</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001509769094138502</v>
+        <v>0.001629583202757801</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.04104699583581208</v>
+        <v>0.03170731707317068</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00209965528047632</v>
+        <v>0.003955978584176023</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004332449160035323</v>
+        <v>0.002829354553492514</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002047677261613656</v>
+        <v>0.0009431181844975489</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0009984399375974951</v>
+        <v>0.004647720544701028</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.005452836101535563</v>
+        <v>0.00734681737061268</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00499702558001196</v>
+        <v>0.001546698393813173</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001120613388380964</v>
+        <v>0.002536125036862325</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.008022498519834175</v>
+        <v>0.006601539372409704</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003966844286560056</v>
+        <v>0.007371225577264629</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002545131695767933</v>
+        <v>0.003167554766133784</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.006800376057662161</v>
+        <v>0.008536585365853621</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.0001768346595933057</v>
+        <v>0.000235779546124415</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003133813851456946</v>
+        <v>0.0003056234718826767</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002042628774422695</v>
+        <v>0.002693901716992286</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001894865525672329</v>
+        <v>0.002742553818932525</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.003399596658023674</v>
+        <v>0.003955978584176023</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0009731642583308386</v>
+        <v>0.001606186793575215</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00386674598453306</v>
+        <v>0.009147424511545299</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.00328596802841914</v>
+        <v>0.005269390171699251</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002042024267534736</v>
+        <v>0.005239786856127892</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001827291482463855</v>
+        <v>0.0008557457212714281</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.001516954193932229</v>
+        <v>0.002538389219680393</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002338661930136132</v>
+        <v>0.00858496151568976</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0009714822939517198</v>
+        <v>0.001710409908581623</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002381698527107479</v>
+        <v>0.006838365896980459</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.000208209399167214</v>
+        <v>8.923259964306318e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001923646049126926</v>
+        <v>0.001591511936339573</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.001742053789730991</v>
+        <v>0.0006914433880725768</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002414425427872824</v>
+        <v>0.003514669926650405</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.003666562206204938</v>
+        <v>0.002042628774422739</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.002888299440023556</v>
+        <v>0.003514669926650393</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0004423473901503772</v>
+        <v>0.0002368265245707657</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.006837606837606813</v>
+        <v>0.003345174659561889</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.003276131045241792</v>
+        <v>0.001092043681747312</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001310452418096719</v>
+        <v>0.002914446881855248</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.003463338533541316</v>
+        <v>0.00183374083129586</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0006189213085764589</v>
+        <v>0.000384843102427479</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003271861986913094</v>
+        <v>0.0003249630723781372</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0005640864932622836</v>
+        <v>0.001894865525672407</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.002706722189173172</v>
+        <v>0.0009815585960737173</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001769389560601553</v>
+        <v>3.120124804992796e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001466458658346304</v>
+        <v>0.001886236368995053</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.004627173592690792</v>
+        <v>0.003863167207313512</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.00499219968798752</v>
+        <v>0.0009470257472624754</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.00110053539559789</v>
+        <v>0.0003552397868561208</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001945181255526041</v>
+        <v>0.001805802249851962</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001887348864641658</v>
+        <v>0.0007334963325183796</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.002944675788221351</v>
+        <v>0.002278780704350358</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.003820293398532959</v>
+        <v>0.003178484107579494</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002416740347774804</v>
+        <v>0.004015466983938088</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.002871521610420325</v>
+        <v>0.003183023872679091</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002359186080802078</v>
+        <v>0.00230905861456483</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0002960331557134044</v>
+        <v>0.0002652519893899696</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001797819039198323</v>
+        <v>0.00100265408434097</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002620904836193439</v>
+        <v>0.001154446177847157</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.002433697347893904</v>
+        <v>0.002505157677571512</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0006581009088060142</v>
+        <v>0.002101835405565411</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0009141846063107862</v>
+        <v>0.0002184087363494958</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0002808112324492629</v>
+        <v>0.0005013270421704852</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0003120124804991686</v>
+        <v>0.0001184132622853884</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001660921341272303</v>
+        <v>0.001296456352636122</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.00118564742589703</v>
+        <v>0.002901716068642812</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0006581009088060142</v>
+        <v>0.001539372409709894</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0005908419497784312</v>
+        <v>0.001535568787214081</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.004586583463338512</v>
+        <v>0.0005327019828351487</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0008257151282807018</v>
+        <v>0.0006723716381418443</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.00109499852027225</v>
+        <v>0.001933372992266469</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001466992665036648</v>
+        <v>0.001834862385321068</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002536674816625872</v>
+        <v>0.001160023795359866</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0008288928359975967</v>
+        <v>0.002220248667850788</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0004736530491414537</v>
+        <v>0.000265878877400294</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.002279455298993449</v>
+        <v>0.00169225947978694</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001041046995835859</v>
+        <v>0.0003255401006214798</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0002592912705272621</v>
+        <v>0.001356531996461285</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0006050129645635893</v>
+        <v>0.001769389560601653</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.002300206428782015</v>
+        <v>0.001391355831853169</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002624594514892331</v>
+        <v>0.0008257151282807795</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001880288310874167</v>
+        <v>0.0004992199687987697</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.000115240564678798</v>
+        <v>0.001091123562371055</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.000118413262285344</v>
+        <v>0.0002592912705271733</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0007400828892835665</v>
+        <v>0.001249256395002929</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0007372456502506175</v>
+        <v>0.00444049733570161</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0002881014116969949</v>
+        <v>0.0002359186080802544</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0003551346552234325</v>
+        <v>0.0002367564368156216</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001120613388380976</v>
+        <v>0.002945785020369818</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001238572692421069</v>
+        <v>0.001420959147424494</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0004033419763757373</v>
+        <v>0.0004143237644273379</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.000532859680284159</v>
+        <v>0.001222493887530585</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0005622965374371014</v>
+        <v>0.002141582391433616</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0003536693191865226</v>
+        <v>0.0006864274570983153</v>
       </c>
     </row>
   </sheetData>
